--- a/AAAGameData/DataTables/CombatRuleTable.xlsx
+++ b/AAAGameData/DataTables/CombatRuleTable.xlsx
@@ -1221,7 +1221,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="1">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>

--- a/AAAGameData/DataTables/CombatRuleTable.xlsx
+++ b/AAAGameData/DataTables/CombatRuleTable.xlsx
@@ -1245,7 +1245,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/CombatRuleTable.xlsx
+++ b/AAAGameData/DataTables/CombatRuleTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1230,7 +1230,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1">
         <v>0.3</v>
